--- a/Team-Data/2008-09/12-24-2008-09.xlsx
+++ b/Team-Data/2008-09/12-24-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>2.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -769,13 +836,13 @@
         <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO2" t="n">
         <v>24</v>
       </c>
       <c r="AP2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ2" t="n">
         <v>26</v>
@@ -799,7 +866,7 @@
         <v>22</v>
       </c>
       <c r="AX2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY2" t="n">
         <v>7</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -843,58 +910,58 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.929</v>
+        <v>0.931</v>
       </c>
       <c r="H3" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I3" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J3" t="n">
-        <v>76.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.487</v>
+        <v>0.486</v>
       </c>
       <c r="L3" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
         <v>16</v>
       </c>
       <c r="N3" t="n">
-        <v>0.379</v>
+        <v>0.374</v>
       </c>
       <c r="O3" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="P3" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.765</v>
+        <v>0.76</v>
       </c>
       <c r="R3" t="n">
         <v>10.9</v>
       </c>
       <c r="S3" t="n">
-        <v>32.6</v>
+        <v>32.4</v>
       </c>
       <c r="T3" t="n">
-        <v>43.5</v>
+        <v>43.3</v>
       </c>
       <c r="U3" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="V3" t="n">
         <v>16.3</v>
@@ -903,25 +970,25 @@
         <v>8.699999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>102.8</v>
+        <v>102.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -933,13 +1000,13 @@
         <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI3" t="n">
         <v>10</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AK3" t="n">
         <v>2</v>
@@ -951,7 +1018,7 @@
         <v>22</v>
       </c>
       <c r="AN3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AO3" t="n">
         <v>2</v>
@@ -960,40 +1027,40 @@
         <v>2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AR3" t="n">
         <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU3" t="n">
         <v>6</v>
       </c>
-      <c r="AU3" t="n">
-        <v>5</v>
-      </c>
       <c r="AV3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW3" t="n">
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA3" t="n">
         <v>1</v>
       </c>
       <c r="BB3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC3" t="n">
         <v>2</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE4" t="n">
         <v>22</v>
@@ -1115,7 +1182,7 @@
         <v>23</v>
       </c>
       <c r="AH4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1160,7 +1227,7 @@
         <v>18</v>
       </c>
       <c r="AW4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX4" t="n">
         <v>20</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -1207,61 +1274,61 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
         <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.444</v>
+        <v>0.464</v>
       </c>
       <c r="H5" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I5" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J5" t="n">
-        <v>84.90000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.443</v>
+        <v>0.445</v>
       </c>
       <c r="L5" t="n">
         <v>6.1</v>
       </c>
       <c r="M5" t="n">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.376</v>
+        <v>0.377</v>
       </c>
       <c r="O5" t="n">
-        <v>18.8</v>
+        <v>19.3</v>
       </c>
       <c r="P5" t="n">
-        <v>23.4</v>
+        <v>24.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.803</v>
+        <v>0.8</v>
       </c>
       <c r="R5" t="n">
         <v>11.9</v>
       </c>
       <c r="S5" t="n">
-        <v>30.6</v>
+        <v>30.4</v>
       </c>
       <c r="T5" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U5" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="V5" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W5" t="n">
         <v>7.8</v>
@@ -1270,22 +1337,22 @@
         <v>5.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>19.9</v>
+        <v>20.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>100.1</v>
+        <v>100.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.8</v>
+        <v>-2.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1297,16 +1364,16 @@
         <v>18</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI5" t="n">
         <v>8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AL5" t="n">
         <v>17</v>
@@ -1315,28 +1382,28 @@
         <v>21</v>
       </c>
       <c r="AN5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AP5" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AV5" t="n">
         <v>20</v>
@@ -1351,16 +1418,16 @@
         <v>24</v>
       </c>
       <c r="AZ5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -1389,85 +1456,85 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6" t="n">
         <v>24</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.889</v>
+        <v>0.857</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>38.6</v>
+        <v>38.2</v>
       </c>
       <c r="J6" t="n">
-        <v>79.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.483</v>
+        <v>0.481</v>
       </c>
       <c r="L6" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M6" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0.343</v>
+        <v>0.339</v>
       </c>
       <c r="O6" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="P6" t="n">
-        <v>24.3</v>
+        <v>24.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.78</v>
+        <v>0.778</v>
       </c>
       <c r="R6" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="S6" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T6" t="n">
         <v>42.1</v>
       </c>
       <c r="U6" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="V6" t="n">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="W6" t="n">
         <v>8</v>
       </c>
       <c r="X6" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="AB6" t="n">
-        <v>102.9</v>
+        <v>102.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>13.7</v>
+        <v>13</v>
       </c>
       <c r="AD6" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1482,37 +1549,37 @@
         <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK6" t="n">
         <v>3</v>
       </c>
       <c r="AL6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP6" t="n">
         <v>12</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>11</v>
       </c>
       <c r="AR6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AT6" t="n">
         <v>13</v>
@@ -1521,25 +1588,25 @@
         <v>15</v>
       </c>
       <c r="AV6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW6" t="n">
         <v>8</v>
       </c>
       <c r="AX6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY6" t="n">
         <v>1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA6" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BB6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -1649,13 +1716,13 @@
         <v>2.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
       </c>
       <c r="AF7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG7" t="n">
         <v>11</v>
@@ -1667,7 +1734,7 @@
         <v>7</v>
       </c>
       <c r="AJ7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK7" t="n">
         <v>14</v>
@@ -1706,13 +1773,13 @@
         <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX7" t="n">
         <v>15</v>
       </c>
       <c r="AY7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ7" t="n">
         <v>2</v>
@@ -1721,7 +1788,7 @@
         <v>28</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -1831,16 +1898,16 @@
         <v>3.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
         <v>6</v>
       </c>
       <c r="AF8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
         <v>24</v>
@@ -1861,7 +1928,7 @@
         <v>16</v>
       </c>
       <c r="AN8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1900,7 +1967,7 @@
         <v>22</v>
       </c>
       <c r="BA8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB8" t="n">
         <v>7</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2086,7 @@
         <v>14</v>
       </c>
       <c r="AF9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG9" t="n">
         <v>13</v>
@@ -2034,7 +2101,7 @@
         <v>22</v>
       </c>
       <c r="AK9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL9" t="n">
         <v>21</v>
@@ -2043,16 +2110,16 @@
         <v>26</v>
       </c>
       <c r="AN9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR9" t="n">
         <v>23</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -2210,19 +2277,19 @@
         <v>9</v>
       </c>
       <c r="AI10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ10" t="n">
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL10" t="n">
         <v>19</v>
       </c>
       <c r="AM10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN10" t="n">
         <v>26</v>
@@ -2243,7 +2310,7 @@
         <v>18</v>
       </c>
       <c r="AT10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU10" t="n">
         <v>24</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
         <v>5</v>
@@ -2398,7 +2465,7 @@
         <v>18</v>
       </c>
       <c r="AK11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL11" t="n">
         <v>8</v>
@@ -2428,7 +2495,7 @@
         <v>8</v>
       </c>
       <c r="AU11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV11" t="n">
         <v>12</v>
@@ -2452,7 +2519,7 @@
         <v>15</v>
       </c>
       <c r="BC11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
         <v>22</v>
@@ -2583,7 +2650,7 @@
         <v>17</v>
       </c>
       <c r="AL12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM12" t="n">
         <v>10</v>
@@ -2598,7 +2665,7 @@
         <v>28</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR12" t="n">
         <v>6</v>
@@ -2607,10 +2674,10 @@
         <v>2</v>
       </c>
       <c r="AT12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV12" t="n">
         <v>26</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-5.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2759,7 +2826,7 @@
         <v>18</v>
       </c>
       <c r="AJ13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK13" t="n">
         <v>29</v>
@@ -2789,10 +2856,10 @@
         <v>17</v>
       </c>
       <c r="AT13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV13" t="n">
         <v>19</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F14" t="n">
         <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.821</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="J14" t="n">
-        <v>84.09999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>0.472</v>
@@ -2872,31 +2939,31 @@
         <v>6.7</v>
       </c>
       <c r="M14" t="n">
-        <v>18.1</v>
+        <v>17.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.369</v>
+        <v>0.376</v>
       </c>
       <c r="O14" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="P14" t="n">
-        <v>28</v>
+        <v>27.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.762</v>
+        <v>0.764</v>
       </c>
       <c r="R14" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S14" t="n">
-        <v>32.4</v>
+        <v>32.6</v>
       </c>
       <c r="T14" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
       <c r="U14" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V14" t="n">
         <v>14.2</v>
@@ -2911,19 +2978,19 @@
         <v>4.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.4</v>
+        <v>107</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.1</v>
+        <v>9.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2941,7 +3008,7 @@
         <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK14" t="n">
         <v>5</v>
@@ -2950,28 +3017,28 @@
         <v>14</v>
       </c>
       <c r="AM14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AN14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AO14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP14" t="n">
         <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
         <v>5</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AT14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="n">
         <v>2</v>
@@ -2983,13 +3050,13 @@
         <v>1</v>
       </c>
       <c r="AX14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
         <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA14" t="n">
         <v>6</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-5.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE15" t="n">
         <v>24</v>
@@ -3135,7 +3202,7 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO15" t="n">
         <v>14</v>
@@ -3144,7 +3211,7 @@
         <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR15" t="n">
         <v>26</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3329,7 +3396,7 @@
         <v>29</v>
       </c>
       <c r="AR16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS16" t="n">
         <v>26</v>
@@ -3353,10 +3420,10 @@
         <v>8</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB16" t="n">
         <v>18</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E17" t="n">
         <v>14</v>
       </c>
       <c r="F17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>0.483</v>
+        <v>0.467</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
@@ -3409,73 +3476,73 @@
         <v>36.3</v>
       </c>
       <c r="J17" t="n">
-        <v>82.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="K17" t="n">
-        <v>0.437</v>
+        <v>0.439</v>
       </c>
       <c r="L17" t="n">
         <v>5</v>
       </c>
       <c r="M17" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0.334</v>
+        <v>0.337</v>
       </c>
       <c r="O17" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="P17" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.775</v>
+        <v>0.774</v>
       </c>
       <c r="R17" t="n">
         <v>13</v>
       </c>
       <c r="S17" t="n">
-        <v>31.1</v>
+        <v>30.7</v>
       </c>
       <c r="T17" t="n">
-        <v>44.1</v>
+        <v>43.7</v>
       </c>
       <c r="U17" t="n">
         <v>21</v>
       </c>
       <c r="V17" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W17" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X17" t="n">
         <v>3.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>97.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>16</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
         <v>17</v>
@@ -3490,7 +3557,7 @@
         <v>9</v>
       </c>
       <c r="AK17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL17" t="n">
         <v>25</v>
@@ -3514,7 +3581,7 @@
         <v>4</v>
       </c>
       <c r="AS17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AT17" t="n">
         <v>5</v>
@@ -3526,25 +3593,25 @@
         <v>21</v>
       </c>
       <c r="AW17" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
       </c>
       <c r="BA17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB17" t="n">
         <v>16</v>
       </c>
       <c r="BC17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-7.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
         <v>28</v>
@@ -3687,7 +3754,7 @@
         <v>15</v>
       </c>
       <c r="AP18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ18" t="n">
         <v>18</v>
@@ -3720,7 +3787,7 @@
         <v>23</v>
       </c>
       <c r="BA18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-2.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -3854,7 +3921,7 @@
         <v>13</v>
       </c>
       <c r="AK19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL19" t="n">
         <v>7</v>
@@ -3863,10 +3930,10 @@
         <v>6</v>
       </c>
       <c r="AN19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP19" t="n">
         <v>7</v>
@@ -3893,7 +3960,7 @@
         <v>25</v>
       </c>
       <c r="AX19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY19" t="n">
         <v>23</v>
@@ -3908,7 +3975,7 @@
         <v>10</v>
       </c>
       <c r="BC19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -4033,10 +4100,10 @@
         <v>29</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL20" t="n">
         <v>6</v>
@@ -4048,7 +4115,7 @@
         <v>1</v>
       </c>
       <c r="AO20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP20" t="n">
         <v>23</v>
@@ -4090,7 +4157,7 @@
         <v>22</v>
       </c>
       <c r="BC20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -4197,13 +4264,13 @@
         <v>-3.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AE21" t="n">
         <v>20</v>
       </c>
       <c r="AF21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG21" t="n">
         <v>20</v>
@@ -4260,7 +4327,7 @@
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ21" t="n">
         <v>6</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-9.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE22" t="n">
         <v>30</v>
@@ -4409,7 +4476,7 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO22" t="n">
         <v>22</v>
@@ -4421,7 +4488,7 @@
         <v>25</v>
       </c>
       <c r="AR22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS22" t="n">
         <v>19</v>
@@ -4436,7 +4503,7 @@
         <v>24</v>
       </c>
       <c r="AW22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX22" t="n">
         <v>23</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -4561,10 +4628,10 @@
         <v>6.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF23" t="n">
         <v>4</v>
@@ -4582,7 +4649,7 @@
         <v>19</v>
       </c>
       <c r="AK23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL23" t="n">
         <v>2</v>
@@ -4591,10 +4658,10 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO23" t="n">
         <v>11</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>10</v>
       </c>
       <c r="AP23" t="n">
         <v>6</v>
@@ -4609,7 +4676,7 @@
         <v>4</v>
       </c>
       <c r="AT23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU23" t="n">
         <v>29</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -4743,13 +4810,13 @@
         <v>-1.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF24" t="n">
         <v>18</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>19</v>
       </c>
       <c r="AG24" t="n">
         <v>19</v>
@@ -4776,10 +4843,10 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ24" t="n">
         <v>24</v>
@@ -4788,7 +4855,7 @@
         <v>2</v>
       </c>
       <c r="AS24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT24" t="n">
         <v>4</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -4925,13 +4992,13 @@
         <v>0.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AE25" t="n">
         <v>11</v>
       </c>
       <c r="AF25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG25" t="n">
         <v>11</v>
@@ -4943,7 +5010,7 @@
         <v>5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK25" t="n">
         <v>1</v>
@@ -4952,7 +5019,7 @@
         <v>9</v>
       </c>
       <c r="AM25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN25" t="n">
         <v>2</v>
@@ -4979,7 +5046,7 @@
         <v>12</v>
       </c>
       <c r="AV25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW25" t="n">
         <v>27</v>
@@ -4991,7 +5058,7 @@
         <v>8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA25" t="n">
         <v>8</v>
@@ -5000,7 +5067,7 @@
         <v>4</v>
       </c>
       <c r="BC25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -5029,55 +5096,55 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E26" t="n">
         <v>18</v>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G26" t="n">
-        <v>0.643</v>
+        <v>0.621</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
       </c>
       <c r="I26" t="n">
-        <v>36.8</v>
+        <v>36.5</v>
       </c>
       <c r="J26" t="n">
-        <v>79.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.461</v>
+        <v>0.456</v>
       </c>
       <c r="L26" t="n">
         <v>8.1</v>
       </c>
       <c r="M26" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.391</v>
+        <v>0.392</v>
       </c>
       <c r="O26" t="n">
-        <v>18.6</v>
+        <v>18.2</v>
       </c>
       <c r="P26" t="n">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.785</v>
+        <v>0.781</v>
       </c>
       <c r="R26" t="n">
         <v>13.4</v>
       </c>
       <c r="S26" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="T26" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="U26" t="n">
         <v>21.1</v>
@@ -5089,46 +5156,46 @@
         <v>6.8</v>
       </c>
       <c r="X26" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>100.1</v>
+        <v>99.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="AD26" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AE26" t="n">
         <v>6</v>
       </c>
       <c r="AF26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AH26" t="n">
         <v>7</v>
       </c>
       <c r="AI26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AL26" t="n">
         <v>5</v>
@@ -5140,19 +5207,19 @@
         <v>4</v>
       </c>
       <c r="AO26" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AP26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT26" t="n">
         <v>16</v>
@@ -5173,16 +5240,16 @@
         <v>2</v>
       </c>
       <c r="AZ26" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB26" t="n">
         <v>14</v>
       </c>
-      <c r="BA26" t="n">
-        <v>16</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>13</v>
-      </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE27" t="n">
         <v>27</v>
@@ -5301,7 +5368,7 @@
         <v>27</v>
       </c>
       <c r="AH27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI27" t="n">
         <v>11</v>
@@ -5328,7 +5395,7 @@
         <v>25</v>
       </c>
       <c r="AQ27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR27" t="n">
         <v>24</v>
@@ -5358,7 +5425,7 @@
         <v>28</v>
       </c>
       <c r="BA27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB27" t="n">
         <v>17</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>3.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
@@ -5486,7 +5553,7 @@
         <v>3</v>
       </c>
       <c r="AI28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ28" t="n">
         <v>21</v>
@@ -5525,7 +5592,7 @@
         <v>9</v>
       </c>
       <c r="AV28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW28" t="n">
         <v>30</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
@@ -5674,7 +5741,7 @@
         <v>19</v>
       </c>
       <c r="AK29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL29" t="n">
         <v>16</v>
@@ -5683,10 +5750,10 @@
         <v>20</v>
       </c>
       <c r="AN29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP29" t="n">
         <v>24</v>
@@ -5698,7 +5765,7 @@
         <v>30</v>
       </c>
       <c r="AS29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT29" t="n">
         <v>27</v>
@@ -5713,7 +5780,7 @@
         <v>28</v>
       </c>
       <c r="AX29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY29" t="n">
         <v>16</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5974,7 @@
         <v>3</v>
       </c>
       <c r="BB30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6120,7 @@
         <v>21</v>
       </c>
       <c r="AP31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ31" t="n">
         <v>20</v>
@@ -6068,7 +6135,7 @@
         <v>22</v>
       </c>
       <c r="AU31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-24-2008-09</t>
+          <t>2008-12-24</t>
         </is>
       </c>
     </row>
